--- a/dataset/construct/dataset_splits/data_size/20_percent/tum/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/tum/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1314</v>
+        <v>2513</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,94 +625,94 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79.1469129464852</v>
+        <v>84.37595016731311</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.6755002704164</v>
       </c>
       <c r="E2" t="n">
-        <v>31.833910034602</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>392.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1150</v>
+        <v>407.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>215.7</v>
       </c>
       <c r="K2" t="n">
-        <v>120.5</v>
+        <v>1015.4</v>
       </c>
       <c r="L2" t="n">
-        <v>175.9</v>
+        <v>52.4</v>
       </c>
       <c r="M2" t="n">
-        <v>229.1</v>
+        <v>28.3</v>
       </c>
       <c r="N2" t="n">
-        <v>525.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>35.9</v>
+        <v>80.7</v>
       </c>
       <c r="P2" t="n">
-        <v>28.7</v>
+        <v>24.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>92.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>25.53</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>25.0017500819378</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.270676691729323</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.2869875222816</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.3675988578761</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -739,22 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>106</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>246</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2008</v>
+        <v>2583</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.27327024235051</v>
+        <v>85.0467322926965</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>26.2975778546712</v>
       </c>
       <c r="E3" t="n">
-        <v>26.4462809917355</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>664</v>
       </c>
       <c r="I3" t="n">
-        <v>34000</v>
+        <v>401</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>245.9</v>
+        <v>1383</v>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>59.7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>359.5</v>
+        <v>95</v>
       </c>
       <c r="O3" t="n">
-        <v>46.7</v>
+        <v>140</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>62.8</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.65</v>
       </c>
       <c r="V3" t="n">
-        <v>6.1</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>24.8281130634072</v>
       </c>
       <c r="X3" t="n">
-        <v>23.75</v>
+        <v>24.3439993862133</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.207547169811321</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.6822001527884</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.3621512301397</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -852,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -861,22 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>555</v>
+        <v>2886</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,79 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82.8866092478516</v>
+        <v>87.4232017960808</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>31.3145661157024</v>
       </c>
       <c r="E4" t="n">
-        <v>26.4235698242832</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>569</v>
       </c>
       <c r="I4" t="n">
-        <v>1160</v>
+        <v>741</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>592</v>
       </c>
       <c r="K4" t="n">
-        <v>236</v>
+        <v>1902</v>
       </c>
       <c r="L4" t="n">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="M4" t="n">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="N4" t="n">
-        <v>701</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>390</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>26</v>
+        <v>24.35</v>
       </c>
       <c r="V4" t="n">
-        <v>26</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>23.9686783804431</v>
       </c>
       <c r="X4" t="n">
-        <v>23.3</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.158102766798419</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.1211849536588</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -965,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -983,24 +954,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>170</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,88 +970,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.4873716632443</v>
+        <v>86.8191345349456</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E5" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>420</v>
       </c>
       <c r="I5" t="n">
-        <v>18300</v>
+        <v>285</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>1013</v>
       </c>
       <c r="L5" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2609</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X5" t="n">
-        <v>25.3</v>
+        <v>23.4220054480732</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.255172413793103</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.6028939368547</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1098,31 +1060,24 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>601</v>
+        <v>500</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,123 +1085,112 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.0775420184044</v>
+        <v>71.47246748802191</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>24.1671624033313</v>
       </c>
       <c r="E6" t="n">
-        <v>22.9004724889498</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>168.7</v>
       </c>
       <c r="I6" t="n">
-        <v>8530</v>
+        <v>83</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>128.9</v>
       </c>
       <c r="K6" t="n">
-        <v>764</v>
+        <v>380.6</v>
       </c>
       <c r="L6" t="n">
-        <v>756</v>
+        <v>23.7</v>
       </c>
       <c r="M6" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2072</v>
+        <v>12.6</v>
       </c>
       <c r="O6" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25.3692386045327</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24.7150115381059</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>93</v>
       </c>
-      <c r="P6" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>78</v>
-      </c>
-      <c r="R6" t="n">
-        <v>246</v>
-      </c>
-      <c r="S6" t="n">
-        <v>34</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>44</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.278810408921933</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>23.8731856378915</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>22.9831467948561</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>116</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>128</v>
-      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>340</v>
+        <v>656</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,41 +1198,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79.8069135485588</v>
+        <v>86.7305080868</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>21.3406795224977</v>
       </c>
       <c r="E7" t="n">
-        <v>27.6816608996539</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>286.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>357.2</v>
+      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>166.4</v>
       </c>
       <c r="K7" t="n">
-        <v>520</v>
+        <v>810.4</v>
       </c>
       <c r="L7" t="n">
-        <v>304</v>
+        <v>12.2</v>
       </c>
       <c r="M7" t="n">
-        <v>172</v>
+        <v>28.3</v>
       </c>
       <c r="N7" t="n">
-        <v>996</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>46.2</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1297,37 +1243,37 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.7458619811561</v>
       </c>
       <c r="X7" t="n">
-        <v>25.75</v>
+        <v>23.5115010765807</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.217993079584775</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>25.528393175452</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>25.055148236001</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1339,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1351,24 +1297,13 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>91</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>180</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2607</v>
+        <v>1228</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,43 +1311,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>81.77774745227769</v>
+        <v>85.5069068623723</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>32.4556777151202</v>
       </c>
       <c r="E8" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>39.8</v>
       </c>
       <c r="I8" t="n">
-        <v>536</v>
+        <v>30.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>26.9</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1421,34 +1356,34 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21.55</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>0.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X8" t="n">
-        <v>23.5</v>
+        <v>21.3554558707986</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.272058823529412</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.5867074102368</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.8860247016979</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1469,30 +1404,21 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1500,85 +1426,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.2467825500038</v>
+        <v>84.97033370725281</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>30.1109905115367</v>
       </c>
       <c r="E9" t="n">
-        <v>30.3460743801652</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I9" t="n">
-        <v>3370</v>
+        <v>152</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="K9" t="n">
-        <v>242.8</v>
+        <v>561</v>
       </c>
       <c r="L9" t="n">
-        <v>371.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>285.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>899.4</v>
+        <v>98</v>
       </c>
       <c r="O9" t="n">
-        <v>72.3</v>
+        <v>98</v>
       </c>
       <c r="P9" t="n">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>264.3</v>
+        <v>96</v>
       </c>
       <c r="S9" t="n">
-        <v>22.6</v>
+        <v>96</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>53.2</v>
+        <v>24.3</v>
       </c>
       <c r="V9" t="n">
-        <v>75.8</v>
+        <v>0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X9" t="n">
-        <v>26.9</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.16382252559727</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.8217134966894</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1590,31 +1516,24 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>914</v>
+        <v>1427</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,79 +1541,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.0671732958146</v>
+        <v>86.99098473901689</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>25.2080856123662</v>
       </c>
       <c r="E10" t="n">
-        <v>25.7629805786761</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>319.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>264.3</v>
       </c>
       <c r="K10" t="n">
-        <v>855</v>
+        <v>786.8</v>
       </c>
       <c r="L10" t="n">
-        <v>534</v>
+        <v>36.6</v>
       </c>
       <c r="M10" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>36.6</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>93</v>
+        <v>22.35</v>
       </c>
       <c r="V10" t="n">
-        <v>93</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>23.0137509549274</v>
       </c>
       <c r="X10" t="n">
-        <v>29</v>
+        <v>22.1512191514658</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.220858895705522</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.921059332824</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>29.2679951700071</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1715,28 +1634,21 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
         <v>154</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2106</v>
+        <v>1314</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,77 +1656,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>87.3656652597156</v>
+        <v>79.1469129464852</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>31.833910034602</v>
       </c>
       <c r="E11" t="n">
-        <v>29.0858725761772</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>120.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>175.9</v>
+      </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>229.1</v>
       </c>
       <c r="K11" t="n">
-        <v>327.7</v>
+        <v>525.5</v>
       </c>
       <c r="L11" t="n">
-        <v>332.3</v>
+        <v>35.9</v>
       </c>
       <c r="M11" t="n">
-        <v>320.1</v>
+        <v>28.7</v>
       </c>
       <c r="N11" t="n">
-        <v>980.1</v>
+        <v>27.5</v>
       </c>
       <c r="O11" t="n">
-        <v>19.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>24.2869875222816</v>
       </c>
       <c r="X11" t="n">
-        <v>27.45</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.26813880126183</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>27.0244461420932</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.4032150535234</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1841,18 +1755,9 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
